--- a/cVAE/results.xlsx
+++ b/cVAE/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,55 +496,50 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>location_h</t>
+          <t>location_i</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>location_i</t>
+          <t>location_j</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>location_j</t>
+          <t>rmse_location_1</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>rmse_location_1</t>
+          <t>rmse_location_2</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>rmse_location_2</t>
+          <t>total_rmse</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>total_rmse</t>
+          <t>model_parameters</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model_parameters</t>
+          <t>loss_computation</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>loss_computation</t>
+          <t>final_total_loss</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>final_total_loss</t>
+          <t>final_recon_loss</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>final_recon_loss</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>final_kl_loss</t>
         </is>
@@ -556,7 +551,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-11-25 15:55:20</t>
+          <t>2025-11-26 09:06:03</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -589,43 +584,42 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>24.6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>0.4081199424999393</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9243181198540706</v>
+        <v>0.3851182991145176</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8706884364873366</v>
+        <v>0.3966191208072285</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8975032781707036</v>
-      </c>
-      <c r="T2" t="n">
         <v>8705952</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>physical_space</t>
         </is>
       </c>
+      <c r="U2" t="n">
+        <v>24.98318862915039</v>
+      </c>
       <c r="V2" t="n">
-        <v>23.22515869140625</v>
+        <v>8.067477226257324</v>
       </c>
       <c r="W2" t="n">
-        <v>6.884922504425049</v>
-      </c>
-      <c r="X2" t="n">
-        <v>408.5059204101562</v>
+        <v>422.892822265625</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-11-26 08:23:45</t>
+          <t>2025-11-26 09:20:43</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -667,43 +661,42 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>24.6</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>0.2881655231998548</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.076513427125802</v>
+        <v>0.2682772167664882</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9975029328681198</v>
+        <v>0.2782213699831715</v>
       </c>
       <c r="S3" t="n">
-        <v>1.037008179996961</v>
-      </c>
-      <c r="T3" t="n">
         <v>8705952</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>physical_space</t>
         </is>
       </c>
+      <c r="U3" t="n">
+        <v>116.9476852416992</v>
+      </c>
       <c r="V3" t="n">
-        <v>39.81136322021484</v>
+        <v>101.3569412231445</v>
       </c>
       <c r="W3" t="n">
-        <v>22.65966415405273</v>
-      </c>
-      <c r="X3" t="n">
-        <v>428.7925415039062</v>
+        <v>389.7686462402344</v>
       </c>
     </row>
     <row r="4">
@@ -712,7 +705,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-11-26 08:31:44</t>
+          <t>2025-11-26 09:21:46</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -750,38 +743,37 @@
       <c r="M4" t="n">
         <v>61.4</v>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>1.042318682738427</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.919102725472832</v>
+        <v>0.9698511811492071</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8682819118706394</v>
+        <v>1.006084931943817</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8936923186717357</v>
-      </c>
-      <c r="T4" t="n">
         <v>8705952</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>physical_space</t>
         </is>
       </c>
+      <c r="U4" t="n">
+        <v>46.63053894042969</v>
+      </c>
       <c r="V4" t="n">
-        <v>24.50717544555664</v>
+        <v>29.35497665405273</v>
       </c>
       <c r="W4" t="n">
-        <v>8.72502613067627</v>
-      </c>
-      <c r="X4" t="n">
-        <v>394.5537109375</v>
+        <v>431.8891296386719</v>
       </c>
     </row>
     <row r="5">
@@ -790,7 +782,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-11-26 08:33:09</t>
+          <t>2025-11-26 09:22:43</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -823,43 +815,42 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>85.7</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>1.257768713030333</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3473751018832954</v>
+        <v>1.18049786281065</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3259876507739744</v>
+        <v>1.219133287920491</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3366813763286349</v>
-      </c>
-      <c r="T5" t="n">
         <v>8705952</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>physical_space</t>
         </is>
       </c>
+      <c r="U5" t="n">
+        <v>30.16899871826172</v>
+      </c>
       <c r="V5" t="n">
-        <v>27.72261810302734</v>
+        <v>13.9555025100708</v>
       </c>
       <c r="W5" t="n">
-        <v>10.57275485992432</v>
-      </c>
-      <c r="X5" t="n">
-        <v>428.7466125488281</v>
+        <v>405.3374328613281</v>
       </c>
     </row>
     <row r="6">
@@ -868,11 +859,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-11-26 08:38:09</t>
+          <t>2025-11-26 09:28:49</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>4096</v>
@@ -901,43 +892,119 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>85.7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
+        <v>1.358995084784604</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.262854606317535</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.310924845551069</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4273584</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>physical_space</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>11.14511108398438</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4.287298679351807</v>
+      </c>
+      <c r="W6" t="n">
+        <v>171.4453277587891</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-11-26 09:29:45</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0.3830181985509535</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.3599799049538115</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3714990517523825</v>
-      </c>
-      <c r="T6" t="n">
-        <v>8705952</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="P7" t="n">
+        <v>1.347151410620943</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.253437985052783</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.300294697836863</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4273584</v>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>physical_space</t>
         </is>
       </c>
-      <c r="V6" t="n">
-        <v>32.64864349365234</v>
-      </c>
-      <c r="W6" t="n">
-        <v>15.45730018615723</v>
-      </c>
-      <c r="X6" t="n">
-        <v>429.7836303710938</v>
+      <c r="U7" t="n">
+        <v>11.25999450683594</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5.155780792236328</v>
+      </c>
+      <c r="W7" t="n">
+        <v>152.6053314208984</v>
       </c>
     </row>
   </sheetData>

--- a/cVAE/results.xlsx
+++ b/cVAE/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1005,6 +1005,622 @@
       </c>
       <c r="W7" t="n">
         <v>152.6053314208984</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-11-26 09:49:29</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>100</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.292920624629227</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.208162425202355</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.250541524915791</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4273584</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>physical_space</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>8.801451683044434</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.678728580474854</v>
+      </c>
+      <c r="W8" t="n">
+        <v>153.0680847167969</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-11-26 09:58:29</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>100</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.346956931156444</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.253433972389805</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.300195451773125</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4273584</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>physical_space</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>12.23091697692871</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.940062522888184</v>
+      </c>
+      <c r="W9" t="n">
+        <v>182.2713775634766</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-11-26 10:01:11</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.351424034025567</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.256905297726466</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.304164665876017</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4273584</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>physical_space</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>33.29153823852539</v>
+      </c>
+      <c r="V10" t="n">
+        <v>26.52292633056641</v>
+      </c>
+      <c r="W10" t="n">
+        <v>169.2152862548828</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-11-26 10:03:15</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.485544550769361</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.370147452412168</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.427846001590765</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4273584</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>physical_space</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>10.04879570007324</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.626098155975342</v>
+      </c>
+      <c r="W11" t="n">
+        <v>160.5674438476562</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-11-26 10:03:57</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I12" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.368277249900788</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.270452578808675</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.319364914354732</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4273584</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>physical_space</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>10.79996681213379</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.985552310943604</v>
+      </c>
+      <c r="W12" t="n">
+        <v>170.3603820800781</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-11-26 10:04:56</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.340261860104326</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.246941871904126</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.293601866004226</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4273584</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>physical_space</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>21.05329513549805</v>
+      </c>
+      <c r="V13" t="n">
+        <v>14.18215942382812</v>
+      </c>
+      <c r="W13" t="n">
+        <v>171.7784118652344</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-11-26 10:08:00</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.493364432916283</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.376467576187348</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.434916004551815</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4273584</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>physical_space</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>9.452305793762207</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.221874237060547</v>
+      </c>
+      <c r="W14" t="n">
+        <v>180.7607879638672</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-11-26 10:08:57</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.230127052416884</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.156755319447052</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.193441185931968</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4273584</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>physical_space</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>14.14873790740967</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.284656524658203</v>
+      </c>
+      <c r="W15" t="n">
+        <v>146.6020355224609</v>
       </c>
     </row>
   </sheetData>

--- a/cVAE/results.xlsx
+++ b/cVAE/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,11 +551,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-11-26 09:06:03</t>
+          <t>2025-11-26 10:24:57</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
         <v>4096</v>
@@ -596,16 +596,16 @@
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4081199424999393</v>
+        <v>0.2800452904598616</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3851182991145176</v>
+        <v>0.2586103294409565</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3966191208072285</v>
+        <v>0.2693278099504091</v>
       </c>
       <c r="S2" t="n">
-        <v>8705952</v>
+        <v>4281312</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>24.98318862915039</v>
+        <v>16.05839157104492</v>
       </c>
       <c r="V2" t="n">
-        <v>8.067477226257324</v>
+        <v>3.328147172927856</v>
       </c>
       <c r="W2" t="n">
-        <v>422.892822265625</v>
+        <v>318.2561340332031</v>
       </c>
     </row>
     <row r="3">
@@ -628,11 +628,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-11-26 09:20:43</t>
+          <t>2025-11-26 10:25:37</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>4096</v>
@@ -673,16 +673,16 @@
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2881655231998548</v>
+        <v>0.3585014496839552</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2682772167664882</v>
+        <v>0.3328047097008717</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2782213699831715</v>
+        <v>0.3456530796924134</v>
       </c>
       <c r="S3" t="n">
-        <v>8705952</v>
+        <v>4276160</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>116.9476852416992</v>
+        <v>14.55660820007324</v>
       </c>
       <c r="V3" t="n">
-        <v>101.3569412231445</v>
+        <v>5.127906799316406</v>
       </c>
       <c r="W3" t="n">
-        <v>389.7686462402344</v>
+        <v>235.717529296875</v>
       </c>
     </row>
     <row r="4">
@@ -705,11 +705,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-11-26 09:21:46</t>
+          <t>2025-11-26 10:26:14</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>4096</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>61.4</v>
+        <v>24.6</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -750,16 +750,16 @@
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.042318682738427</v>
+        <v>0.3051495274049677</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9698511811492071</v>
+        <v>0.2838485586823888</v>
       </c>
       <c r="R4" t="n">
-        <v>1.006084931943817</v>
+        <v>0.2944990430436782</v>
       </c>
       <c r="S4" t="n">
-        <v>8705952</v>
+        <v>4273584</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>46.63053894042969</v>
+        <v>21.73014450073242</v>
       </c>
       <c r="V4" t="n">
-        <v>29.35497665405273</v>
+        <v>15.35014820098877</v>
       </c>
       <c r="W4" t="n">
-        <v>431.8891296386719</v>
+        <v>159.4998931884766</v>
       </c>
     </row>
     <row r="5">
@@ -782,11 +782,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-11-26 09:22:43</t>
+          <t>2025-11-26 10:27:54</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
         <v>4096</v>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>85.7</v>
+        <v>24.6</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
@@ -827,16 +827,16 @@
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.257768713030333</v>
+        <v>0.3142597400026544</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.18049786281065</v>
+        <v>0.2914555911426788</v>
       </c>
       <c r="R5" t="n">
-        <v>1.219133287920491</v>
+        <v>0.3028576655726666</v>
       </c>
       <c r="S5" t="n">
-        <v>8705952</v>
+        <v>4281312</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>30.16899871826172</v>
+        <v>34.7413330078125</v>
       </c>
       <c r="V5" t="n">
-        <v>13.9555025100708</v>
+        <v>20.53216552734375</v>
       </c>
       <c r="W5" t="n">
-        <v>405.3374328613281</v>
+        <v>355.2291870117188</v>
       </c>
     </row>
     <row r="6">
@@ -859,11 +859,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-11-26 09:28:49</t>
+          <t>2025-11-26 10:28:46</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
         <v>4096</v>
@@ -892,10 +892,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>85.7</v>
+        <v>61.4</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
@@ -904,16 +904,16 @@
         <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.358995084784604</v>
+        <v>1.010320646195293</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.262854606317535</v>
+        <v>0.9392199254029125</v>
       </c>
       <c r="R6" t="n">
-        <v>1.310924845551069</v>
+        <v>0.9747702857991027</v>
       </c>
       <c r="S6" t="n">
-        <v>4273584</v>
+        <v>4281312</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -921,13 +921,13 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>11.14511108398438</v>
+        <v>20.15595436096191</v>
       </c>
       <c r="V6" t="n">
-        <v>4.287298679351807</v>
+        <v>5.455639839172363</v>
       </c>
       <c r="W6" t="n">
-        <v>171.4453277587891</v>
+        <v>367.5078735351562</v>
       </c>
     </row>
     <row r="7">
@@ -936,11 +936,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-11-26 09:29:45</t>
+          <t>2025-11-26 10:29:30</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
         <v>4096</v>
@@ -981,16 +981,16 @@
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.347151410620943</v>
+        <v>1.214221135405526</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.253437985052783</v>
+        <v>1.142441073776046</v>
       </c>
       <c r="R7" t="n">
-        <v>1.300294697836863</v>
+        <v>1.178331104590786</v>
       </c>
       <c r="S7" t="n">
-        <v>4273584</v>
+        <v>4281312</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>11.25999450683594</v>
+        <v>96.55656433105469</v>
       </c>
       <c r="V7" t="n">
-        <v>5.155780792236328</v>
+        <v>85.29804992675781</v>
       </c>
       <c r="W7" t="n">
-        <v>152.6053314208984</v>
+        <v>281.462890625</v>
       </c>
     </row>
     <row r="8">
@@ -1013,11 +1013,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-11-26 09:49:29</t>
+          <t>2025-11-26 10:53:24</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
         <v>4096</v>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>85.7</v>
+        <v>24.6</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -1058,16 +1058,16 @@
         <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.292920624629227</v>
+        <v>0.2933385560247055</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.208162425202355</v>
+        <v>0.2755121969960803</v>
       </c>
       <c r="R8" t="n">
-        <v>1.250541524915791</v>
+        <v>0.2844253765103929</v>
       </c>
       <c r="S8" t="n">
-        <v>4273584</v>
+        <v>4281312</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>8.801451683044434</v>
+        <v>357.4508056640625</v>
       </c>
       <c r="V8" t="n">
-        <v>2.678728580474854</v>
+        <v>279.6071472167969</v>
       </c>
       <c r="W8" t="n">
-        <v>153.0680847167969</v>
+        <v>1946.091552734375</v>
       </c>
     </row>
     <row r="9">
@@ -1090,11 +1090,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-11-26 09:58:29</t>
+          <t>2025-11-26 10:54:20</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
         <v>4096</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>85.7</v>
+        <v>61.4</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1135,16 +1135,16 @@
         <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.346956931156444</v>
+        <v>0.9007878735502607</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.253433972389805</v>
+        <v>0.8274060941983213</v>
       </c>
       <c r="R9" t="n">
-        <v>1.300195451773125</v>
+        <v>0.864096983874291</v>
       </c>
       <c r="S9" t="n">
-        <v>4273584</v>
+        <v>4281312</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>12.23091697692871</v>
+        <v>378.0645141601562</v>
       </c>
       <c r="V9" t="n">
-        <v>4.940062522888184</v>
+        <v>301.1898803710938</v>
       </c>
       <c r="W9" t="n">
-        <v>182.2713775634766</v>
+        <v>1921.8662109375</v>
       </c>
     </row>
     <row r="10">
@@ -1167,11 +1167,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-11-26 10:01:11</t>
+          <t>2025-11-26 10:59:45</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D10" t="n">
         <v>4096</v>
@@ -1212,16 +1212,16 @@
         <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.351424034025567</v>
+        <v>1.32433994419228</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.256905297726466</v>
+        <v>1.243384757669311</v>
       </c>
       <c r="R10" t="n">
-        <v>1.304164665876017</v>
+        <v>1.283862350930796</v>
       </c>
       <c r="S10" t="n">
-        <v>4273584</v>
+        <v>4281312</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>33.29153823852539</v>
+        <v>475.0914611816406</v>
       </c>
       <c r="V10" t="n">
-        <v>26.52292633056641</v>
+        <v>396.3123779296875</v>
       </c>
       <c r="W10" t="n">
-        <v>169.2152862548828</v>
+        <v>1969.47705078125</v>
       </c>
     </row>
     <row r="11">
@@ -1244,11 +1244,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-11-26 10:03:15</t>
+          <t>2025-11-26 11:04:33</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
         <v>4096</v>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>85.7</v>
+        <v>24.6</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
@@ -1289,30 +1289,30 @@
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.485544550769361</v>
+        <v>0.323275243838227</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.370147452412168</v>
+        <v>0.3020155809273824</v>
       </c>
       <c r="R11" t="n">
-        <v>1.427846001590765</v>
+        <v>0.3126454123828047</v>
       </c>
       <c r="S11" t="n">
-        <v>4273584</v>
+        <v>4281312</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>physical_space</t>
+          <t>modal_space</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>10.04879570007324</v>
+        <v>342.5973510742188</v>
       </c>
       <c r="V11" t="n">
-        <v>3.626098155975342</v>
+        <v>264.5730590820312</v>
       </c>
       <c r="W11" t="n">
-        <v>160.5674438476562</v>
+        <v>1950.60693359375</v>
       </c>
     </row>
     <row r="12">
@@ -1321,11 +1321,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-11-26 10:03:57</t>
+          <t>2025-11-26 11:05:17</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
         <v>4096</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>85.7</v>
+        <v>61.4</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
@@ -1366,30 +1366,30 @@
         <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.368277249900788</v>
+        <v>0.929093334616905</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.270452578808675</v>
+        <v>0.8571950965206983</v>
       </c>
       <c r="R12" t="n">
-        <v>1.319364914354732</v>
+        <v>0.8931442155688016</v>
       </c>
       <c r="S12" t="n">
-        <v>4273584</v>
+        <v>4281312</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>physical_space</t>
+          <t>modal_space</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>10.79996681213379</v>
+        <v>366.9605712890625</v>
       </c>
       <c r="V12" t="n">
-        <v>3.985552310943604</v>
+        <v>295.8821411132812</v>
       </c>
       <c r="W12" t="n">
-        <v>170.3603820800781</v>
+        <v>1776.960693359375</v>
       </c>
     </row>
     <row r="13">
@@ -1398,11 +1398,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-11-26 10:04:56</t>
+          <t>2025-11-26 11:08:00</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D13" t="n">
         <v>4096</v>
@@ -1443,30 +1443,30 @@
         <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.340261860104326</v>
+        <v>1.269668050065522</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.246941871904126</v>
+        <v>1.200982607521665</v>
       </c>
       <c r="R13" t="n">
-        <v>1.293601866004226</v>
+        <v>1.235325328793593</v>
       </c>
       <c r="S13" t="n">
-        <v>4273584</v>
+        <v>4281312</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>physical_space</t>
+          <t>modal_space</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>21.05329513549805</v>
+        <v>342.7147216796875</v>
       </c>
       <c r="V13" t="n">
-        <v>14.18215942382812</v>
+        <v>272.336181640625</v>
       </c>
       <c r="W13" t="n">
-        <v>171.7784118652344</v>
+        <v>1759.463256835938</v>
       </c>
     </row>
     <row r="14">
@@ -1475,11 +1475,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-11-26 10:08:00</t>
+          <t>2025-11-26 11:35:30</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D14" t="n">
         <v>4096</v>
@@ -1494,7 +1494,7 @@
         <v>1200</v>
       </c>
       <c r="H14" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>100</v>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>85.7</v>
+        <v>24.6</v>
       </c>
       <c r="N14" t="n">
         <v>2</v>
@@ -1520,30 +1520,30 @@
         <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.493364432916283</v>
+        <v>0.197843402422114</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.376467576187348</v>
+        <v>0.1843957724727484</v>
       </c>
       <c r="R14" t="n">
-        <v>1.434916004551815</v>
+        <v>0.1911195874474312</v>
       </c>
       <c r="S14" t="n">
-        <v>4273584</v>
+        <v>4281312</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>physical_space</t>
+          <t>modal_space</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>9.452305793762207</v>
+        <v>1019.808288574219</v>
       </c>
       <c r="V14" t="n">
-        <v>2.221874237060547</v>
+        <v>895.63671875</v>
       </c>
       <c r="W14" t="n">
-        <v>180.7607879638672</v>
+        <v>124.1715545654297</v>
       </c>
     </row>
     <row r="15">
@@ -1552,11 +1552,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-11-26 10:08:57</t>
+          <t>2025-11-26 11:36:21</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
         <v>4096</v>
@@ -1571,7 +1571,7 @@
         <v>1200</v>
       </c>
       <c r="H15" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>100</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>85.7</v>
+        <v>61.4</v>
       </c>
       <c r="N15" t="n">
         <v>2</v>
@@ -1597,30 +1597,492 @@
         <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.230127052416884</v>
+        <v>0.5215424418862937</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.156755319447052</v>
+        <v>0.506577868300802</v>
       </c>
       <c r="R15" t="n">
-        <v>1.193441185931968</v>
+        <v>0.5140601550935479</v>
       </c>
       <c r="S15" t="n">
-        <v>4273584</v>
+        <v>4281312</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>physical_space</t>
+          <t>modal_space</t>
         </is>
       </c>
       <c r="U15" t="n">
-        <v>14.14873790740967</v>
+        <v>846.4580078125</v>
       </c>
       <c r="V15" t="n">
-        <v>8.284656524658203</v>
+        <v>545.5169067382812</v>
       </c>
       <c r="W15" t="n">
-        <v>146.6020355224609</v>
+        <v>300.9410705566406</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-11-26 11:37:10</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>32</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>100</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.3514083966523787</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.5348029786301223</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4431056876412505</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4281312</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>modal_space</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>671.8721923828125</v>
+      </c>
+      <c r="V16" t="n">
+        <v>528.1021118164062</v>
+      </c>
+      <c r="W16" t="n">
+        <v>143.7700958251953</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-11-26 11:54:18</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>32</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.2584265468006845</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.2387045359921301</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2485655413964073</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4281312</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>modal_space</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>1122.232666015625</v>
+      </c>
+      <c r="V17" t="n">
+        <v>864.4203491210938</v>
+      </c>
+      <c r="W17" t="n">
+        <v>429.6872863769531</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-11-26 11:55:01</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>32</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I18" t="n">
+        <v>100</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.1954671075754005</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1842788671413673</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.1898729873583839</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4281312</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>modal_space</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>749.4891357421875</v>
+      </c>
+      <c r="V18" t="n">
+        <v>478.4540100097656</v>
+      </c>
+      <c r="W18" t="n">
+        <v>361.3801574707031</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>21</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-11-26 11:58:51</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>32</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.2300439479603633</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2157428714489978</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2228934097046806</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4281312</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>modal_space</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>778.8248291015625</v>
+      </c>
+      <c r="V19" t="n">
+        <v>510.18994140625</v>
+      </c>
+      <c r="W19" t="n">
+        <v>537.2697143554688</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>22</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-11-26 11:59:50</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>32</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.573046309932609</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5522089439805354</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.5626276269565722</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4281312</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>modal_space</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>642.5445556640625</v>
+      </c>
+      <c r="V20" t="n">
+        <v>415.3168640136719</v>
+      </c>
+      <c r="W20" t="n">
+        <v>454.4554443359375</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-11-26 12:00:43</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>32</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4096</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>100</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>[1, 3, 5, 7]</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.3890766127711831</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.5413130695264629</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.465194841148823</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4281312</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>modal_space</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>573.9827880859375</v>
+      </c>
+      <c r="V21" t="n">
+        <v>413.9104614257812</v>
+      </c>
+      <c r="W21" t="n">
+        <v>320.1446838378906</v>
       </c>
     </row>
   </sheetData>
